--- a/templates/26-kanban-and-wip.xlsx
+++ b/templates/26-kanban-and-wip.xlsx
@@ -216,10 +216,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
             <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'WIP and lead time'!$A$21:$A$22</f>

--- a/templates/26-kanban-and-wip.xlsx
+++ b/templates/26-kanban-and-wip.xlsx
@@ -216,17 +216,33 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="1F4E79"/>
-            </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="1F4E79"/>
-              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3F8F5A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'WIP and lead time'!$A$21:$A$22</f>

--- a/templates/26-kanban-and-wip.xlsx
+++ b/templates/26-kanban-and-wip.xlsx
@@ -299,7 +299,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>

--- a/templates/26-kanban-and-wip.xlsx
+++ b/templates/26-kanban-and-wip.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Lead time today (hours)</t>
@@ -874,6 +874,11 @@
       <c r="B12" s="11">
         <f>IFERROR(B5/B6*24,"")</f>
         <v/>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>The same wait in hours, which is usually the unit your promise and your SLA are written in.</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
@@ -950,7 +955,7 @@
       </c>
     </row>
     <row r="20"/>
-    <row r="21">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Lead time today</t>
@@ -960,8 +965,13 @@
         <f>B11</f>
         <v/>
       </c>
-    </row>
-    <row r="22">
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>What customers actually experience now — the same figure as above, repeated here so the chart can draw it against the promise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Lead time promised</t>
@@ -970,6 +980,11 @@
       <c r="B22" s="11">
         <f>B7</f>
         <v/>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>The wait you want to commit to. The gap between the two bars is backlog, not effort: closing it means capping the work, not pushing the team harder.</t>
+        </is>
       </c>
     </row>
     <row r="23"/>

--- a/templates/26-kanban-and-wip.xlsx
+++ b/templates/26-kanban-and-wip.xlsx
@@ -648,14 +648,14 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Green row</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t>Green cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A worked example so you can see the expected format. Delete it when you start.</t>
+          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
         </is>
       </c>
     </row>

--- a/templates/26-kanban-and-wip.xlsx
+++ b/templates/26-kanban-and-wip.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -93,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -112,6 +117,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -297,7 +305,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -741,13 +749,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -971,7 +988,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Lead time promised</t>
@@ -984,6 +1001,12 @@
       <c r="D22" s="10" t="inlineStr">
         <is>
           <t>The wait you want to commit to. The gap between the two bars is backlog, not effort: closing it means capping the work, not pushing the team harder.</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Actual against commitment, so the gap is the message. Read it with the WIP number on the same tab: lead time is work in progress divided by throughput, so a promise you keep missing is usually a WIP limit you never set.
+SO:  Set a WIP limit rather than asking for more speed. Lead time is work in progress divided by throughput, so a promise you keep missing is usually a queue you never capped.</t>
         </is>
       </c>
     </row>
@@ -1006,9 +1029,10 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="F22:N22"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A10:D10"/>

--- a/templates/26-kanban-and-wip.xlsx
+++ b/templates/26-kanban-and-wip.xlsx
@@ -656,59 +656,47 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Green cells</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>What this is for</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
+          <t>Turning a lead-time promise into a work-in-progress limit you can actually enforce.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>What this is for</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
+          <t>How to use it</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Turning a lead-time promise into a work-in-progress limit you can actually enforce.</t>
+          <t>Enter your open count, your closing rate and the wait you want to promise. The cap that follows is arithmetic — Little's Law — not an opinion.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>How to use it</t>
+          <t>The part people skip</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Enter your open count, your closing rate and the wait you want to promise. The cap that follows is arithmetic — Little's Law — not an opinion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>The part people skip</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="2" t="inlineStr">
-        <is>
           <t>You usually have to clear the excess backlog before the cap can hold. Plan that as a separate push with a start and an end, or the limit gets abandoned in week one.</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
